--- a/specs/teksty-kartochek.xlsx
+++ b/specs/teksty-kartochek.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты карточек" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты услуг" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все карточки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Тексты карточек'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все карточки'!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,13 @@
       <color rgb="007A7A70"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C32F55"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7F7F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE8EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -100,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,13 +483,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -488,12 +504,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Вариант 1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Вариант 2</t>
+          <t>Текст</t>
         </is>
       </c>
     </row>
@@ -513,11 +524,6 @@
           <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Если бухгалтерия отнимает время</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -535,11 +541,6 @@
           <t>Приведём в порядок прошлые периоды</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Если в учёте накопился беспорядок</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -557,11 +558,6 @@
           <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Заполним декларации без ошибок</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -579,11 +575,6 @@
           <t>Разберём вашу ситуацию предметно</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Если есть конкретный вопрос</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -601,11 +592,6 @@
           <t>Для небольших компаний и ИП</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Если штатный бухгалтер пока не нужен</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -623,11 +609,6 @@
           <t>Для растущих компаний</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Когда оборот вырос, а учёт нет</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -645,11 +626,6 @@
           <t>Для компаний с большими оборотами</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Когда нужна команда, а не бухгалтер</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -664,12 +640,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Команда вместо одного человека в штате</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Если ищете главбуха в штат</t>
+          <t>Подберем надежного и эффективного специалиста</t>
         </is>
       </c>
     </row>
@@ -686,11 +657,6 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Покажем реальные цифры бизнеса</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
           <t>Если непонятно, где прибыль</t>
         </is>
       </c>
@@ -711,11 +677,6 @@
           <t>Проверим учёт раньше, чем налоговая</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Если не уверены в своём бухгалтере</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -730,11 +691,6 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Разберём, где вы переплачиваете</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
           <t>Законные способы платить меньше</t>
         </is>
       </c>
@@ -752,11 +708,6 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Когда спор идёт о цифрах</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
           <t>Дадим заключение для суда</t>
         </is>
       </c>
@@ -777,11 +728,6 @@
           <t>Свой юрист без найма в штат</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Договоры, споры и риски — на нас</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -796,11 +742,6 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Если контрагент не платит</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
           <t>От претензии до исполнительного листа</t>
         </is>
       </c>
@@ -818,12 +759,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Найдём риски в документах</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Если давно не проверяли документы</t>
+          <t>Найдём и устраним риски в документах</t>
         </is>
       </c>
     </row>
@@ -840,11 +776,6 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Подготовим и подадим документы</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
           <t>Если меняется директор или адрес</t>
         </is>
       </c>
@@ -862,11 +793,6 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Откроем или закроем компанию</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
           <t>Регистрация ООО и ИП под ключ</t>
         </is>
       </c>
@@ -887,11 +813,6 @@
           <t>Договор, который защитит вас</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Если шаблон из интернета не подходит</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -909,11 +830,6 @@
           <t>Поможем с импортом и экспортом</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Валютный контроль и НДС 0%</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -931,11 +847,6 @@
           <t>Защитим в споре с сотрудником</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Если работник пошёл в суд или ГИТ</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -950,12 +861,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Будем представлять вас в суде</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Если дело дошло до суда</t>
+          <t>Защитим вас в суде</t>
         </is>
       </c>
     </row>
@@ -975,11 +881,6 @@
           <t>Защитим бренд и разработки</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Если ваш знак или контент копируют</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -994,11 +895,6 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Проведём через налоговую проверку</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
           <t>Если пришло требование или проверка</t>
         </is>
       </c>
@@ -1019,11 +915,6 @@
           <t>Ответим на правовой вопрос</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Если нужен совет до решения</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1038,11 +929,6 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Оформим вычет без визита в офис</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
           <t>Если некогда ехать в офис</t>
         </is>
       </c>
@@ -1063,11 +949,6 @@
           <t>Оформим вычет вместе с вами</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Если хотите разобраться лично</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1085,11 +966,6 @@
           <t>Заполним и подадим за вас</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>3-НДФЛ без ошибок и штрафов</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1104,12 +980,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Закрепим название за вами</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Если боитесь, что название займут</t>
+          <t>Зарегистрируем бренд</t>
         </is>
       </c>
     </row>
@@ -1129,14 +1000,8 @@
           <t>Возьмём воинский учёт на себя</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Если нет кадровика для этой задачи</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -1170,4 +1035,2405 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Страница, где стоит блок</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Карточка</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Текст под названием</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Акцентная</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Свой текст</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Увидеть цифры, а не только отчётность</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Если за прошлые годы беспорядок</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Чтобы учёт больше не разваливался</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Проверим, всё ли теперь в порядке</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Если проверка уже на пороге</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Если сдавать нужно регулярно</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Проверим учёт раньше, чем налоговая</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Разберём вашу ситуацию предметно</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Если вопрос оказался не разовым</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Проверим учёт раньше, чем налоговая</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Ответим на правовой вопрос</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Возьмём учёт и отчётность на себя</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация ООО и ИП под ключ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Возьмём учёт и отчётность на себя</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Если непонятно, где прибыль</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Подберем надежного и эффективного специалиста</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Возьмём учёт и отчётность на себя</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Если непонятно, где прибыль</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Поможем с импортом и экспортом</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Команда дешевле главбуха в штате</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Если непонятно, где прибыль</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Для растущих компаний</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Нужен тот, кто будет вести учёт</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Проверим учёт раньше, чем налоговая</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Исправим и возьмём учёт на себя</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Если непонятно, где прибыль</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Закроем то, что нашёл аудит</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Схему нужно корректно вести</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Проверим учёт раньше, чем налоговая</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Если непонятно, где прибыль</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Проведём через проверку ФНС</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Проверим учёт раньше, чем налоговая</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Спор ведёт юрист, а не эксперт</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Защитим вас в суде</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия и юристы в одном месте</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Договор, который защитит вас</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Защитим вас в суде</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Договор, который защитит вас</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Подтвердим сумму долга расчётом</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Учётные риски закроем тоже</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Если пришло требование или проверка</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Проверим ещё и бухгалтерию</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация ООО и ИП под ключ</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Договор, который защитит вас</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Сменили директора — смените и бухгалтера</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия с первого дня компании</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Для небольших компаний и ИП</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Если меняется директор или адрес</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Поможем с импортом и экспортом</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Учёт ВЭД своими силами ведут редко</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Для компаний с большими оборотами</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr"/>
+      <c r="E77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Споры растут из ошибок в расчётах</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Возьмём воинский учёт на себя</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Защитим вас в суде</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr"/>
+      <c r="E81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>От претензии до исполнительного листа</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr"/>
+      <c r="E82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Защитим в споре с сотрудником</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Если спор о цифрах и расчётах</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Зарегистрируем бренд</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr"/>
+      <c r="E87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Защитим вас в суде</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Договор, который защитит вас</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Сменить бухгалтера, пока не поздно</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Проверим учёт до прихода ФНС</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Законные способы платить меньше</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr"/>
+      <c r="E93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>С бухгалтерией поможем тоже</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Договор, который защитит вас</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr"/>
+      <c r="E96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr"/>
+      <c r="E97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Оформим вычет вместе с вами</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
+      <c r="E98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Заполним и подадим за вас</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr"/>
+      <c r="E99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Когда вопрос сложнее вычета</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Подготовим и сдадим отчётность</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr"/>
+      <c r="E101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Если некогда ехать в офис</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr"/>
+      <c r="E102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Заполним и подадим за вас</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Когда вопрос сложнее вычета</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Подготовим и сдадим отчётность</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Если некогда ехать в офис</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Оформим вычет вместе с вами</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Подготовим и сдадим отчётность</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Когда вопрос сложнее вычета</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Защитим бренд и разработки</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация ООО и ИП под ключ</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr"/>
+      <c r="E111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr"/>
+      <c r="E112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Бухгалтерию возьмём на себя</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Кадры и зарплату ведём тоже</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Разберём вашу ситуацию предметно</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr"/>
+      <c r="E116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Защитим в споре с сотрудником</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr"/>
+      <c r="E117" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E117"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>